--- a/outputs/178-22.xlsx
+++ b/outputs/178-22.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="17">
   <si>
     <t xml:space="preserve">SL</t>
   </si>
@@ -148,12 +148,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -349,205 +353,205 @@
   <dimension ref="A1:C18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="17.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="10.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10.33"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="B8" s="0" t="s">
+      <c r="A8" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+      <c r="A9" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
+      <c r="A10" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="2" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
+      <c r="A11" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="n">
+      <c r="A12" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="n">
+      <c r="A13" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="n">
+      <c r="A14" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="n">
+      <c r="A15" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="n">
+      <c r="A16" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="n">
+      <c r="A17" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="n">
+      <c r="A18" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="2" t="s">
         <v>16</v>
       </c>
     </row>
@@ -567,270 +571,73 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A2:C20"/>
+  <dimension ref="A2:C7"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
-        <f aca="false" t="array" ref="A3:A3">IFERROR(INDEX(Sheet1!A$2:$A18,SMALL(IF((Sheet1!B$2:B$18="TELIVISION")+(Sheet1!C$2:C$18="CLASS III")+(Sheet1!C$2:C$18="CLASS IV")&gt;0,ROW(Sheet1!A$2:$A18)-1),ROW()-2)),"")</f>
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="str">
-        <f aca="false" t="array" ref="B3:B3">IFERROR(INDEX(Sheet1!B$2:$B18,SMALL(IF((Sheet1!B$2:B$18="TELIVISION")+(Sheet1!C$2:C$18="CLASS III")+(Sheet1!C$2:C$18="CLASS IV")&gt;0,ROW(Sheet1!B$2:$B18)-1),ROW()-2)),"")</f>
-        <v>CFL</v>
-      </c>
-      <c r="C3" s="0" t="str">
-        <f aca="false" t="array" ref="C3:C3">IFERROR(INDEX(Sheet1!C$2:$C18,SMALL(IF((Sheet1!B$2:B$18="TELIVISION")+(Sheet1!C$2:C$18="CLASS III")+(Sheet1!C$2:C$18="CLASS IV")&gt;0,ROW(Sheet1!C$2:$C18)-1),ROW()-2)),"")</f>
-        <v>CLASS IV</v>
+      <c r="B3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
-        <f aca="false" t="array" ref="A4:A4">IFERROR(INDEX(Sheet1!A$2:$A18,SMALL(IF((Sheet1!B$2:B$18="TELIVISION")+(Sheet1!C$2:C$18="CLASS III")+(Sheet1!C$2:C$18="CLASS IV")&gt;0,ROW(Sheet1!A$2:$A18)-1),ROW()-2)),"")</f>
+      <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="0" t="str">
-        <f aca="false" t="array" ref="B4:B4">IFERROR(INDEX(Sheet1!B$2:$B18,SMALL(IF((Sheet1!B$2:B$18="TELIVISION")+(Sheet1!C$2:C$18="CLASS III")+(Sheet1!C$2:C$18="CLASS IV")&gt;0,ROW(Sheet1!B$2:$B18)-1),ROW()-2)),"")</f>
-        <v>TELIVISION</v>
-      </c>
-      <c r="C4" s="0" t="str">
-        <f aca="false" t="array" ref="C4:C4">IFERROR(INDEX(Sheet1!C$2:$C18,SMALL(IF((Sheet1!B$2:B$18="TELIVISION")+(Sheet1!C$2:C$18="CLASS III")+(Sheet1!C$2:C$18="CLASS IV")&gt;0,ROW(Sheet1!C$2:$C18)-1),ROW()-2)),"")</f>
-        <v>CLASS II</v>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
-        <f aca="false" t="array" ref="A5:A5">IFERROR(INDEX(Sheet1!A$2:$A18,SMALL(IF((Sheet1!B$2:B$18="TELIVISION")+(Sheet1!C$2:C$18="CLASS III")+(Sheet1!C$2:C$18="CLASS IV")&gt;0,ROW(Sheet1!A$2:$A18)-1),ROW()-2)),"")</f>
+      <c r="A5" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B5" s="0" t="str">
-        <f aca="false" t="array" ref="B5:B5">IFERROR(INDEX(Sheet1!B$2:$B18,SMALL(IF((Sheet1!B$2:B$18="TELIVISION")+(Sheet1!C$2:C$18="CLASS III")+(Sheet1!C$2:C$18="CLASS IV")&gt;0,ROW(Sheet1!B$2:$B18)-1),ROW()-2)),"")</f>
-        <v>MIXTER</v>
-      </c>
-      <c r="C5" s="0" t="str">
-        <f aca="false" t="array" ref="C5:C5">IFERROR(INDEX(Sheet1!C$2:$C18,SMALL(IF((Sheet1!B$2:B$18="TELIVISION")+(Sheet1!C$2:C$18="CLASS III")+(Sheet1!C$2:C$18="CLASS IV")&gt;0,ROW(Sheet1!C$2:$C18)-1),ROW()-2)),"")</f>
-        <v>CLASS III</v>
+      <c r="B5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
-        <f aca="false" t="array" ref="A6:A6">IFERROR(INDEX(Sheet1!A$2:$A18,SMALL(IF((Sheet1!B$2:B$18="TELIVISION")+(Sheet1!C$2:C$18="CLASS III")+(Sheet1!C$2:C$18="CLASS IV")&gt;0,ROW(Sheet1!A$2:$A18)-1),ROW()-2)),"")</f>
+      <c r="A6" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="B6" s="0" t="str">
-        <f aca="false" t="array" ref="B6:B6">IFERROR(INDEX(Sheet1!B$2:$B18,SMALL(IF((Sheet1!B$2:B$18="TELIVISION")+(Sheet1!C$2:C$18="CLASS III")+(Sheet1!C$2:C$18="CLASS IV")&gt;0,ROW(Sheet1!B$2:$B18)-1),ROW()-2)),"")</f>
-        <v>CFL</v>
-      </c>
-      <c r="C6" s="0" t="str">
-        <f aca="false" t="array" ref="C6:C6">IFERROR(INDEX(Sheet1!C$2:$C18,SMALL(IF((Sheet1!B$2:B$18="TELIVISION")+(Sheet1!C$2:C$18="CLASS III")+(Sheet1!C$2:C$18="CLASS IV")&gt;0,ROW(Sheet1!C$2:$C18)-1),ROW()-2)),"")</f>
-        <v>CLASS IV</v>
+      <c r="B6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
-        <f aca="false" t="array" ref="A7:A7">IFERROR(INDEX(Sheet1!A$2:$A18,SMALL(IF((Sheet1!B$2:B$18="TELIVISION")+(Sheet1!C$2:C$18="CLASS III")+(Sheet1!C$2:C$18="CLASS IV")&gt;0,ROW(Sheet1!A$2:$A18)-1),ROW()-2)),"")</f>
+      <c r="A7" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="B7" s="0" t="str">
-        <f aca="false" t="array" ref="B7:B7">IFERROR(INDEX(Sheet1!B$2:$B18,SMALL(IF((Sheet1!B$2:B$18="TELIVISION")+(Sheet1!C$2:C$18="CLASS III")+(Sheet1!C$2:C$18="CLASS IV")&gt;0,ROW(Sheet1!B$2:$B18)-1),ROW()-2)),"")</f>
-        <v>MIXTER</v>
-      </c>
-      <c r="C7" s="0" t="str">
-        <f aca="false" t="array" ref="C7:C7">IFERROR(INDEX(Sheet1!C$2:$C18,SMALL(IF((Sheet1!B$2:B$18="TELIVISION")+(Sheet1!C$2:C$18="CLASS III")+(Sheet1!C$2:C$18="CLASS IV")&gt;0,ROW(Sheet1!C$2:$C18)-1),ROW()-2)),"")</f>
-        <v>CLASS III</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="str">
-        <f aca="false" t="array" ref="A8:A8">IFERROR(INDEX(Sheet1!A$2:$A18,SMALL(IF((Sheet1!B$2:B$18="TELIVISION")+(Sheet1!C$2:C$18="CLASS III")+(Sheet1!C$2:C$18="CLASS IV")&gt;0,ROW(Sheet1!A$2:$A18)-1),ROW()-2)),"")</f>
-        <v/>
-      </c>
-      <c r="B8" s="0" t="str">
-        <f aca="false" t="array" ref="B8:B8">IFERROR(INDEX(Sheet1!B$2:$B18,SMALL(IF((Sheet1!B$2:B$18="TELIVISION")+(Sheet1!C$2:C$18="CLASS III")+(Sheet1!C$2:C$18="CLASS IV")&gt;0,ROW(Sheet1!B$2:$B18)-1),ROW()-2)),"")</f>
-        <v/>
-      </c>
-      <c r="C8" s="0" t="str">
-        <f aca="false" t="array" ref="C8:C8">IFERROR(INDEX(Sheet1!C$2:$C18,SMALL(IF((Sheet1!B$2:B$18="TELIVISION")+(Sheet1!C$2:C$18="CLASS III")+(Sheet1!C$2:C$18="CLASS IV")&gt;0,ROW(Sheet1!C$2:$C18)-1),ROW()-2)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="str">
-        <f aca="false" t="array" ref="A9:A9">IFERROR(INDEX(Sheet1!A$2:$A18,SMALL(IF((Sheet1!B$2:B$18="TELIVISION")+(Sheet1!C$2:C$18="CLASS III")+(Sheet1!C$2:C$18="CLASS IV")&gt;0,ROW(Sheet1!A$2:$A18)-1),ROW()-2)),"")</f>
-        <v/>
-      </c>
-      <c r="B9" s="0" t="str">
-        <f aca="false" t="array" ref="B9:B9">IFERROR(INDEX(Sheet1!B$2:$B18,SMALL(IF((Sheet1!B$2:B$18="TELIVISION")+(Sheet1!C$2:C$18="CLASS III")+(Sheet1!C$2:C$18="CLASS IV")&gt;0,ROW(Sheet1!B$2:$B18)-1),ROW()-2)),"")</f>
-        <v/>
-      </c>
-      <c r="C9" s="0" t="str">
-        <f aca="false" t="array" ref="C9:C9">IFERROR(INDEX(Sheet1!C$2:$C18,SMALL(IF((Sheet1!B$2:B$18="TELIVISION")+(Sheet1!C$2:C$18="CLASS III")+(Sheet1!C$2:C$18="CLASS IV")&gt;0,ROW(Sheet1!C$2:$C18)-1),ROW()-2)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="str">
-        <f aca="false" t="array" ref="A10:A10">IFERROR(INDEX(Sheet1!A$2:$A18,SMALL(IF((Sheet1!B$2:B$18="TELIVISION")+(Sheet1!C$2:C$18="CLASS III")+(Sheet1!C$2:C$18="CLASS IV")&gt;0,ROW(Sheet1!A$2:$A18)-1),ROW()-2)),"")</f>
-        <v/>
-      </c>
-      <c r="B10" s="0" t="str">
-        <f aca="false" t="array" ref="B10:B10">IFERROR(INDEX(Sheet1!B$2:$B18,SMALL(IF((Sheet1!B$2:B$18="TELIVISION")+(Sheet1!C$2:C$18="CLASS III")+(Sheet1!C$2:C$18="CLASS IV")&gt;0,ROW(Sheet1!B$2:$B18)-1),ROW()-2)),"")</f>
-        <v/>
-      </c>
-      <c r="C10" s="0" t="str">
-        <f aca="false" t="array" ref="C10:C10">IFERROR(INDEX(Sheet1!C$2:$C18,SMALL(IF((Sheet1!B$2:B$18="TELIVISION")+(Sheet1!C$2:C$18="CLASS III")+(Sheet1!C$2:C$18="CLASS IV")&gt;0,ROW(Sheet1!C$2:$C18)-1),ROW()-2)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="str">
-        <f aca="false" t="array" ref="A11:A11">IFERROR(INDEX(Sheet1!A$2:$A18,SMALL(IF((Sheet1!B$2:B$18="TELIVISION")+(Sheet1!C$2:C$18="CLASS III")+(Sheet1!C$2:C$18="CLASS IV")&gt;0,ROW(Sheet1!A$2:$A18)-1),ROW()-2)),"")</f>
-        <v/>
-      </c>
-      <c r="B11" s="0" t="str">
-        <f aca="false" t="array" ref="B11:B11">IFERROR(INDEX(Sheet1!B$2:$B18,SMALL(IF((Sheet1!B$2:B$18="TELIVISION")+(Sheet1!C$2:C$18="CLASS III")+(Sheet1!C$2:C$18="CLASS IV")&gt;0,ROW(Sheet1!B$2:$B18)-1),ROW()-2)),"")</f>
-        <v/>
-      </c>
-      <c r="C11" s="0" t="str">
-        <f aca="false" t="array" ref="C11:C11">IFERROR(INDEX(Sheet1!C$2:$C18,SMALL(IF((Sheet1!B$2:B$18="TELIVISION")+(Sheet1!C$2:C$18="CLASS III")+(Sheet1!C$2:C$18="CLASS IV")&gt;0,ROW(Sheet1!C$2:$C18)-1),ROW()-2)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="str">
-        <f aca="false" t="array" ref="A12:A12">IFERROR(INDEX(Sheet1!A$2:$A18,SMALL(IF((Sheet1!B$2:B$18="TELIVISION")+(Sheet1!C$2:C$18="CLASS III")+(Sheet1!C$2:C$18="CLASS IV")&gt;0,ROW(Sheet1!A$2:$A18)-1),ROW()-2)),"")</f>
-        <v/>
-      </c>
-      <c r="B12" s="0" t="str">
-        <f aca="false" t="array" ref="B12:B12">IFERROR(INDEX(Sheet1!B$2:$B18,SMALL(IF((Sheet1!B$2:B$18="TELIVISION")+(Sheet1!C$2:C$18="CLASS III")+(Sheet1!C$2:C$18="CLASS IV")&gt;0,ROW(Sheet1!B$2:$B18)-1),ROW()-2)),"")</f>
-        <v/>
-      </c>
-      <c r="C12" s="0" t="str">
-        <f aca="false" t="array" ref="C12:C12">IFERROR(INDEX(Sheet1!C$2:$C18,SMALL(IF((Sheet1!B$2:B$18="TELIVISION")+(Sheet1!C$2:C$18="CLASS III")+(Sheet1!C$2:C$18="CLASS IV")&gt;0,ROW(Sheet1!C$2:$C18)-1),ROW()-2)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="str">
-        <f aca="false" t="array" ref="A13:A13">IFERROR(INDEX(Sheet1!A$2:$A18,SMALL(IF((Sheet1!B$2:B$18="TELIVISION")+(Sheet1!C$2:C$18="CLASS III")+(Sheet1!C$2:C$18="CLASS IV")&gt;0,ROW(Sheet1!A$2:$A18)-1),ROW()-2)),"")</f>
-        <v/>
-      </c>
-      <c r="B13" s="0" t="str">
-        <f aca="false" t="array" ref="B13:B13">IFERROR(INDEX(Sheet1!B$2:$B18,SMALL(IF((Sheet1!B$2:B$18="TELIVISION")+(Sheet1!C$2:C$18="CLASS III")+(Sheet1!C$2:C$18="CLASS IV")&gt;0,ROW(Sheet1!B$2:$B18)-1),ROW()-2)),"")</f>
-        <v/>
-      </c>
-      <c r="C13" s="0" t="str">
-        <f aca="false" t="array" ref="C13:C13">IFERROR(INDEX(Sheet1!C$2:$C18,SMALL(IF((Sheet1!B$2:B$18="TELIVISION")+(Sheet1!C$2:C$18="CLASS III")+(Sheet1!C$2:C$18="CLASS IV")&gt;0,ROW(Sheet1!C$2:$C18)-1),ROW()-2)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="str">
-        <f aca="false" t="array" ref="A14:A14">IFERROR(INDEX(Sheet1!A$2:$A18,SMALL(IF((Sheet1!B$2:B$18="TELIVISION")+(Sheet1!C$2:C$18="CLASS III")+(Sheet1!C$2:C$18="CLASS IV")&gt;0,ROW(Sheet1!A$2:$A18)-1),ROW()-2)),"")</f>
-        <v/>
-      </c>
-      <c r="B14" s="0" t="str">
-        <f aca="false" t="array" ref="B14:B14">IFERROR(INDEX(Sheet1!B$2:$B18,SMALL(IF((Sheet1!B$2:B$18="TELIVISION")+(Sheet1!C$2:C$18="CLASS III")+(Sheet1!C$2:C$18="CLASS IV")&gt;0,ROW(Sheet1!B$2:$B18)-1),ROW()-2)),"")</f>
-        <v/>
-      </c>
-      <c r="C14" s="0" t="str">
-        <f aca="false" t="array" ref="C14:C14">IFERROR(INDEX(Sheet1!C$2:$C18,SMALL(IF((Sheet1!B$2:B$18="TELIVISION")+(Sheet1!C$2:C$18="CLASS III")+(Sheet1!C$2:C$18="CLASS IV")&gt;0,ROW(Sheet1!C$2:$C18)-1),ROW()-2)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="str">
-        <f aca="false" t="array" ref="A15:A15">IFERROR(INDEX(Sheet1!A$2:$A18,SMALL(IF((Sheet1!B$2:B$18="TELIVISION")+(Sheet1!C$2:C$18="CLASS III")+(Sheet1!C$2:C$18="CLASS IV")&gt;0,ROW(Sheet1!A$2:$A18)-1),ROW()-2)),"")</f>
-        <v/>
-      </c>
-      <c r="B15" s="0" t="str">
-        <f aca="false" t="array" ref="B15:B15">IFERROR(INDEX(Sheet1!B$2:$B18,SMALL(IF((Sheet1!B$2:B$18="TELIVISION")+(Sheet1!C$2:C$18="CLASS III")+(Sheet1!C$2:C$18="CLASS IV")&gt;0,ROW(Sheet1!B$2:$B18)-1),ROW()-2)),"")</f>
-        <v/>
-      </c>
-      <c r="C15" s="0" t="str">
-        <f aca="false" t="array" ref="C15:C15">IFERROR(INDEX(Sheet1!C$2:$C18,SMALL(IF((Sheet1!B$2:B$18="TELIVISION")+(Sheet1!C$2:C$18="CLASS III")+(Sheet1!C$2:C$18="CLASS IV")&gt;0,ROW(Sheet1!C$2:$C18)-1),ROW()-2)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="str">
-        <f aca="false" t="array" ref="A16:A16">IFERROR(INDEX(Sheet1!A$2:$A18,SMALL(IF((Sheet1!B$2:B$18="TELIVISION")+(Sheet1!C$2:C$18="CLASS III")+(Sheet1!C$2:C$18="CLASS IV")&gt;0,ROW(Sheet1!A$2:$A18)-1),ROW()-2)),"")</f>
-        <v/>
-      </c>
-      <c r="B16" s="0" t="str">
-        <f aca="false" t="array" ref="B16:B16">IFERROR(INDEX(Sheet1!B$2:$B18,SMALL(IF((Sheet1!B$2:B$18="TELIVISION")+(Sheet1!C$2:C$18="CLASS III")+(Sheet1!C$2:C$18="CLASS IV")&gt;0,ROW(Sheet1!B$2:$B18)-1),ROW()-2)),"")</f>
-        <v/>
-      </c>
-      <c r="C16" s="0" t="str">
-        <f aca="false" t="array" ref="C16:C16">IFERROR(INDEX(Sheet1!C$2:$C18,SMALL(IF((Sheet1!B$2:B$18="TELIVISION")+(Sheet1!C$2:C$18="CLASS III")+(Sheet1!C$2:C$18="CLASS IV")&gt;0,ROW(Sheet1!C$2:$C18)-1),ROW()-2)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="str">
-        <f aca="false" t="array" ref="A17:A17">IFERROR(INDEX(Sheet1!A$2:$A18,SMALL(IF((Sheet1!B$2:B$18="TELIVISION")+(Sheet1!C$2:C$18="CLASS III")+(Sheet1!C$2:C$18="CLASS IV")&gt;0,ROW(Sheet1!A$2:$A18)-1),ROW()-2)),"")</f>
-        <v/>
-      </c>
-      <c r="B17" s="0" t="str">
-        <f aca="false" t="array" ref="B17:B17">IFERROR(INDEX(Sheet1!B$2:$B18,SMALL(IF((Sheet1!B$2:B$18="TELIVISION")+(Sheet1!C$2:C$18="CLASS III")+(Sheet1!C$2:C$18="CLASS IV")&gt;0,ROW(Sheet1!B$2:$B18)-1),ROW()-2)),"")</f>
-        <v/>
-      </c>
-      <c r="C17" s="0" t="str">
-        <f aca="false" t="array" ref="C17:C17">IFERROR(INDEX(Sheet1!C$2:$C18,SMALL(IF((Sheet1!B$2:B$18="TELIVISION")+(Sheet1!C$2:C$18="CLASS III")+(Sheet1!C$2:C$18="CLASS IV")&gt;0,ROW(Sheet1!C$2:$C18)-1),ROW()-2)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="str">
-        <f aca="false" t="array" ref="A18:A18">IFERROR(INDEX(Sheet1!A$2:$A18,SMALL(IF((Sheet1!B$2:B$18="TELIVISION")+(Sheet1!C$2:C$18="CLASS III")+(Sheet1!C$2:C$18="CLASS IV")&gt;0,ROW(Sheet1!A$2:$A18)-1),ROW()-2)),"")</f>
-        <v/>
-      </c>
-      <c r="B18" s="0" t="str">
-        <f aca="false" t="array" ref="B18:B18">IFERROR(INDEX(Sheet1!B$2:$B18,SMALL(IF((Sheet1!B$2:B$18="TELIVISION")+(Sheet1!C$2:C$18="CLASS III")+(Sheet1!C$2:C$18="CLASS IV")&gt;0,ROW(Sheet1!B$2:$B18)-1),ROW()-2)),"")</f>
-        <v/>
-      </c>
-      <c r="C18" s="0" t="str">
-        <f aca="false" t="array" ref="C18:C18">IFERROR(INDEX(Sheet1!C$2:$C18,SMALL(IF((Sheet1!B$2:B$18="TELIVISION")+(Sheet1!C$2:C$18="CLASS III")+(Sheet1!C$2:C$18="CLASS IV")&gt;0,ROW(Sheet1!C$2:$C18)-1),ROW()-2)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="str">
-        <f aca="false" t="array" ref="A19:A19">IFERROR(INDEX(Sheet1!A$2:$A18,SMALL(IF((Sheet1!B$2:B$18="TELIVISION")+(Sheet1!C$2:C$18="CLASS III")+(Sheet1!C$2:C$18="CLASS IV")&gt;0,ROW(Sheet1!A$2:$A18)-1),ROW()-2)),"")</f>
-        <v/>
-      </c>
-      <c r="B19" s="0" t="str">
-        <f aca="false" t="array" ref="B19:B19">IFERROR(INDEX(Sheet1!B$2:$B18,SMALL(IF((Sheet1!B$2:B$18="TELIVISION")+(Sheet1!C$2:C$18="CLASS III")+(Sheet1!C$2:C$18="CLASS IV")&gt;0,ROW(Sheet1!B$2:$B18)-1),ROW()-2)),"")</f>
-        <v/>
-      </c>
-      <c r="C19" s="0" t="str">
-        <f aca="false" t="array" ref="C19:C19">IFERROR(INDEX(Sheet1!C$2:$C18,SMALL(IF((Sheet1!B$2:B$18="TELIVISION")+(Sheet1!C$2:C$18="CLASS III")+(Sheet1!C$2:C$18="CLASS IV")&gt;0,ROW(Sheet1!C$2:$C18)-1),ROW()-2)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="str">
-        <f aca="false" t="array" ref="A20:A20">IFERROR(INDEX(Sheet1!A$2:$A18,SMALL(IF((Sheet1!B$2:B$18="TELIVISION")+(Sheet1!C$2:C$18="CLASS III")+(Sheet1!C$2:C$18="CLASS IV")&gt;0,ROW(Sheet1!A$2:$A18)-1),ROW()-2)),"")</f>
-        <v/>
-      </c>
-      <c r="B20" s="0" t="str">
-        <f aca="false" t="array" ref="B20:B20">IFERROR(INDEX(Sheet1!B$2:$B18,SMALL(IF((Sheet1!B$2:B$18="TELIVISION")+(Sheet1!C$2:C$18="CLASS III")+(Sheet1!C$2:C$18="CLASS IV")&gt;0,ROW(Sheet1!B$2:$B18)-1),ROW()-2)),"")</f>
-        <v/>
-      </c>
-      <c r="C20" s="0" t="str">
-        <f aca="false" t="array" ref="C20:C20">IFERROR(INDEX(Sheet1!C$2:$C18,SMALL(IF((Sheet1!B$2:B$18="TELIVISION")+(Sheet1!C$2:C$18="CLASS III")+(Sheet1!C$2:C$18="CLASS IV")&gt;0,ROW(Sheet1!C$2:$C18)-1),ROW()-2)),"")</f>
-        <v/>
+      <c r="B7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
